--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -582,7 +582,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 139 of 191 items resolved  (73%)</t>
+          <t>All-epics progress: 143 of 191 items resolved  (75%)</t>
         </is>
       </c>
     </row>
@@ -635,14 +635,14 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -187,6 +187,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -582,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 143 of 191 items resolved  (75%)</t>
+          <t>All-epics progress: 166 of 212 items resolved  (78%)</t>
         </is>
       </c>
     </row>
@@ -635,14 +638,14 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -722,78 +725,123 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Testing Plan</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Automated tests + Alpha + Beta + GA readiness</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>See Epic 1 Testing Plan sheet</t>
-        </is>
-      </c>
-    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Workflow Engine (turn workflows from data into an engine)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic5_Workflow_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise RBAC (branches + groups + SSO + API keys + portal)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic6_Enterprise_RBAC.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1"/>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Go-Live</t>
+          <t>Testing</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Go-Live Checklist</t>
+          <t>Testing Plan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Final SaaS-scale readiness (billing, alerts, backups)</t>
+          <t>Automated + Alpha + Beta + GA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>See Epic 1 Go-Live Checklist sheet</t>
+          <t>See Epic 1 Testing Plan sheet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Go-Live</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Moving to Next Epic</t>
+          <t>Go-Live Checklist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Items parked from Epic 2 awaiting Epic 4 planning</t>
+          <t>Final SaaS-scale readiness</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>See Epic 2 'Moving to Next Epic' sheet</t>
-        </is>
-      </c>
-    </row>
+          <t>See Epic 1 Go-Live Checklist sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 166 of 212 items resolved  (78%)</t>
+          <t>All-epics progress: 167 of 212 items resolved  (79%)</t>
         </is>
       </c>
     </row>
@@ -638,14 +638,14 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -840,8 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 167 of 212 items resolved  (79%)</t>
+          <t>All-epics progress: 185 of 214 items resolved  (86%)</t>
         </is>
       </c>
     </row>
@@ -737,19 +737,19 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 185 of 214 items resolved  (86%)</t>
+          <t>All-epics progress: 186 of 336 items resolved  (55%)</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,39 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic7_UX_UI_Optimization.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 186 of 336 items resolved  (55%)</t>
+          <t>All-epics progress: 189 of 336 items resolved  (56%)</t>
         </is>
       </c>
     </row>
@@ -803,14 +803,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>122</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 189 of 336 items resolved  (56%)</t>
+          <t>All-epics progress: 202 of 336 items resolved  (60%)</t>
         </is>
       </c>
     </row>
@@ -803,14 +803,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>122</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 202 of 336 items resolved  (60%)</t>
+          <t>All-epics progress: 202 of 349 items resolved  (58%)</t>
         </is>
       </c>
     </row>
@@ -806,11 +806,11 @@
         <v>17</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 202 of 349 items resolved  (58%)</t>
+          <t>All-epics progress: 203 of 350 items resolved  (58%)</t>
         </is>
       </c>
     </row>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 203 of 350 items resolved  (58%)</t>
+          <t>All-epics progress: 207 of 352 items resolved  (59%)</t>
         </is>
       </c>
     </row>
@@ -803,14 +803,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 207 of 352 items resolved  (59%)</t>
+          <t>All-epics progress: 211 of 352 items resolved  (60%)</t>
         </is>
       </c>
     </row>
@@ -803,14 +803,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>138</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 211 of 352 items resolved  (60%)</t>
+          <t>All-epics progress: 249 of 367 items resolved  (68%)</t>
         </is>
       </c>
     </row>
@@ -803,14 +803,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -825,48 +826,73 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Backend Optimization &amp; Modularization (10 sprints; finishes the Phase A/B migration; Sprint 1 = modular foundation + backend analysis)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic8_Backend_Optimization.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Testing Plan</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Automated + Alpha + Beta + GA</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>See Epic 1 Testing Plan sheet</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Go-Live</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Go-Live Checklist</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Final SaaS-scale readiness</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>See Epic 1 Go-Live Checklist sheet</t>
         </is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 249 of 367 items resolved  (68%)</t>
+          <t>All-epics progress: 256 of 375 items resolved  (68%)</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,20 @@
           <t>Backend Optimization &amp; Modularization (10 sprints; finishes the Phase A/B migration; Sprint 1 = modular foundation + backend analysis)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 256 of 375 items resolved  (68%)</t>
+          <t>All-epics progress: 257 of 380 items resolved  (68%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 257 of 380 items resolved  (68%)</t>
+          <t>All-epics progress: 258 of 381 items resolved  (68%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 258 of 381 items resolved  (68%)</t>
+          <t>All-epics progress: 260 of 383 items resolved  (68%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 260 of 383 items resolved  (68%)</t>
+          <t>All-epics progress: 261 of 383 items resolved  (68%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>16</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 261 of 383 items resolved  (68%)</t>
+          <t>All-epics progress: 262 of 383 items resolved  (68%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>16</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 262 of 383 items resolved  (68%)</t>
+          <t>All-epics progress: 263 of 383 items resolved  (69%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>16</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 263 of 383 items resolved  (69%)</t>
+          <t>All-epics progress: 264 of 383 items resolved  (69%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>16</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 264 of 383 items resolved  (69%)</t>
+          <t>All-epics progress: 319 of 442 items resolved  (72%)</t>
         </is>
       </c>
     </row>
@@ -859,48 +859,81 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Landing Page (marketing site -- hero, problem, product tour, ICP, pricing, CEO Brief teaser, final CTA)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic9_Landing_Page.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Testing Plan</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Automated + Alpha + Beta + GA</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>See Epic 1 Testing Plan sheet</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Go-Live</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Go-Live Checklist</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Final SaaS-scale readiness</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>See Epic 1 Go-Live Checklist sheet</t>
         </is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 319 of 442 items resolved  (72%)</t>
+          <t>All-epics progress: 320 of 458 items resolved  (70%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 320 of 458 items resolved  (70%)</t>
+          <t>All-epics progress: 321 of 458 items resolved  (70%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 321 of 458 items resolved  (70%)</t>
+          <t>All-epics progress: 322 of 458 items resolved  (70%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 322 of 458 items resolved  (70%)</t>
+          <t>All-epics progress: 325 of 458 items resolved  (71%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 325 of 458 items resolved  (71%)</t>
+          <t>All-epics progress: 327 of 458 items resolved  (71%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 327 of 458 items resolved  (71%)</t>
+          <t>All-epics progress: 329 of 458 items resolved  (72%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 329 of 458 items resolved  (72%)</t>
+          <t>All-epics progress: 330 of 458 items resolved  (72%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 330 of 458 items resolved  (72%)</t>
+          <t>All-epics progress: 331 of 458 items resolved  (72%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 331 of 458 items resolved  (72%)</t>
+          <t>All-epics progress: 332 of 458 items resolved  (72%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 332 of 458 items resolved  (72%)</t>
+          <t>All-epics progress: 334 of 458 items resolved  (73%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 334 of 458 items resolved  (73%)</t>
+          <t>All-epics progress: 335 of 458 items resolved  (73%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,11 +585,10 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 335 of 458 items resolved  (73%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>All-epics progress: 338 of 472 items resolved  (72%)</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -837,14 +836,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 338 of 472 items resolved  (72%)</t>
+          <t>All-epics progress: 342 of 472 items resolved  (72%)</t>
         </is>
       </c>
     </row>
@@ -836,14 +836,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>46</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 342 of 472 items resolved  (72%)</t>
+          <t>All-epics progress: 349 of 472 items resolved  (74%)</t>
         </is>
       </c>
     </row>
@@ -836,14 +836,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>46</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 349 of 472 items resolved  (74%)</t>
+          <t>All-epics progress: 349 of 488 items resolved  (72%)</t>
         </is>
       </c>
     </row>
@@ -839,11 +839,11 @@
         <v>45</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 349 of 488 items resolved  (72%)</t>
+          <t>All-epics progress: 357 of 488 items resolved  (73%)</t>
         </is>
       </c>
     </row>
@@ -836,14 +836,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>62</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 357 of 488 items resolved  (73%)</t>
+          <t>All-epics progress: 365 of 488 items resolved  (75%)</t>
         </is>
       </c>
     </row>
@@ -836,14 +836,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>62</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 365 of 488 items resolved  (75%)</t>
+          <t>All-epics progress: 375 of 559 items resolved  (67%)</t>
         </is>
       </c>
     </row>
@@ -891,48 +891,81 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Epic 10</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Admin / Platform Console (super-admin console: tenant 360, impersonation, support desk, billing, observability; Sprint 0 = shipped)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic10_Admin_Console.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Testing Plan</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Automated + Alpha + Beta + GA</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>See Epic 1 Testing Plan sheet</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Go-Live</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Go-Live Checklist</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Final SaaS-scale readiness</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>See Epic 1 Go-Live Checklist sheet</t>
         </is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 375 of 559 items resolved  (67%)</t>
+          <t>All-epics progress: 375 of 581 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -700,14 +700,14 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Dex AI Persona + product decisions</t>
+          <t>AI Foundation &amp; Company Intelligence (reshaped from Dex AI Persona: prompt+model+telemetry foundation, extraction engine, Company Brain RAG+agents, Dex persona, evals)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic3_Dex_AI_Persona.xlsx</t>
+          <t>DecisionOS_Epic3_AI_Foundation.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -704,19 +704,19 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -704,14 +704,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -589,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -707,7 +708,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -905,7 +906,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -906,7 +906,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -708,11 +708,11 @@
         <v>14</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -708,11 +708,11 @@
         <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>46</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>46</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>46</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>46</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -708,11 +708,11 @@
         <v>27</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -705,14 +705,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 375 of 581 items resolved  (65%)</t>
+          <t>All-epics progress: 381 of 587 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 381 of 587 items resolved  (65%)</t>
+          <t>All-epics progress: 387 of 593 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 387 of 593 items resolved  (65%)</t>
+          <t>All-epics progress: 393 of 599 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 393 of 599 items resolved  (65%)</t>
+          <t>All-epics progress: 399 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Eng. complete*</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 399 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 400 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>86</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Eng. complete*</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Enterprise RBAC (branches + groups + SSO + API keys + portal)</t>
+          <t>Enterprise RBAC (branches/groups/SSO/API keys/portal) -- DEFERRED to Enterprise Expansion phase; SME-first product does not need it yet</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -778,12 +778,12 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Deferred (future)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 400 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 401 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 401 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 408 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 408 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 414 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 414 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 421 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 421 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 428 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 428 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 434 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 434 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 441 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 441 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 447 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 447 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 452 of 605 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>73</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 319 of 442 items resolved  (72%)</t>
+          <t>All-epics progress: 334 of 457 items resolved  (73%)</t>
         </is>
       </c>
     </row>
@@ -870,14 +870,14 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 452 of 605 items resolved  (65%)</t>
+          <t>All-epics progress: 453 of 606 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 453 of 606 items resolved  (65%)</t>
+          <t>All-epics progress: 494 of 648 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -804,14 +804,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -729,7 +729,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Epic 5</t>
+          <t>Epic 4</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -755,14 +755,14 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic5_Workflow_Engine.xlsx</t>
+          <t>DecisionOS_Epic4_Workflow_Engine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Epic 6</t>
+          <t>Epic 5</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -788,14 +788,14 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic6_Enterprise_RBAC.xlsx</t>
+          <t>DecisionOS_Epic5_Enterprise_RBAC.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Epic 7</t>
+          <t>Epic 6</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -821,14 +821,14 @@
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic7_UX_UI_Optimization.xlsx</t>
+          <t>DecisionOS_Epic6_UX_UI_Optimization.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Epic 8</t>
+          <t>Epic 7</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
@@ -854,14 +854,14 @@
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic8_Backend_Optimization.xlsx</t>
+          <t>DecisionOS_Epic7_Backend_Optimization.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
@@ -887,14 +887,14 @@
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic9_Landing_Page.xlsx</t>
+          <t>DecisionOS_Epic8_Landing_Page.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Epic 10</t>
+          <t>Epic 9</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic10_Admin_Console.xlsx</t>
+          <t>DecisionOS_Epic9_Admin_Console.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 494 of 648 items resolved  (65%)</t>
+          <t>All-epics progress: 506 of 648 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -804,14 +804,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>195</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 506 of 648 items resolved  (65%)</t>
+          <t>All-epics progress: 518 of 782 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>74</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -925,9 +925,35 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Testing</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Epic 10</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Testing (comprehensive scenario coverage: unit + functional + role-matrix + onboarding + multi-niche + team-scale + formula-edge + isolation + AI/extraction + concurrency + regression-health + E2E; 12 sprints)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>134</v>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic10_Testing.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 518 of 782 items resolved  (65%)</t>
+          <t>All-epics progress: 518 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -932,14 +932,14 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Testing (comprehensive scenario coverage: unit + functional + role-matrix + onboarding + multi-niche + team-scale + formula-edge + isolation + AI/extraction + concurrency + regression-health + E2E; 12 sprints)</t>
+          <t>Testing (comprehensive scenario coverage: unit + functional + role-matrix + onboarding + multi-niche + team-scale + formula-edge + isolation + AI/extraction + concurrency + regression-health + E2E; 13 sprints)</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 518 of 802 items resolved  (65%)</t>
+          <t>All-epics progress: 532 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 532 of 802 items resolved  (65%)</t>
+          <t>All-epics progress: 539 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -936,14 +936,14 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 539 of 802 items resolved  (65%)</t>
+          <t>All-epics progress: 540 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -936,14 +936,14 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 540 of 802 items resolved  (65%)</t>
+          <t>All-epics progress: 543 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -936,14 +936,14 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 543 of 802 items resolved  (65%)</t>
+          <t>All-epics progress: 545 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -936,14 +936,14 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 545 of 802 items resolved  (65%)</t>
+          <t>All-epics progress: 548 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -936,14 +936,14 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 548 of 802 items resolved  (65%)</t>
+          <t>All-epics progress: 549 of 802 items resolved  (65%)</t>
         </is>
       </c>
     </row>
@@ -936,14 +936,14 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -589,7 +589,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -705,19 +704,19 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -807,11 +806,11 @@
         <v>117</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -936,19 +935,19 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>154</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -589,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -638,14 +639,14 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
